--- a/NV_year1_awardees.xlsx
+++ b/NV_year1_awardees.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="1186">
   <si>
     <t xml:space="preserve">READ THIS FIRST</t>
   </si>
@@ -2391,6 +2391,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cybersecurity for four rural hospitals through a shared CIO model and a pilot program with Grover C. Dils for endpoint protection and email security. Service area: Lincoln, Lyon, Mineral, Humboldt. Published by the Nevada Health Authority on its RHT Funded Projects - Budget Period 1 page, which names every subrecipient and PUBLISHES NO AMOUNT FOR ANY OF THEM. NVHA has published NO round total for this pool, so `round_amount` is empty. Source snapshot: 2026-09-24.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMOUNT_PRELIMINARY;ASSOCIATION_SERVICE</t>
   </si>
   <si>
     <t xml:space="preserve">OWNER RULING (session 102, NV_BP1_FOLLOWUPS (1)): takes the NRHPF ruling of session 101 -- PASS_THROUGH_DESIGNATED, Yes, POOL_NAMED_HOSPITALS, LOW, intermediary Nevada Rural Hospital Partners Foundation, Inc.. The line's service area is 'Lincoln, Lyon, Mineral, Humboldt Counties' and its project is 'Cybersecurity for four rural hospitals through a shared CIO model and a pilot program with Grover C. Dils for endpoint protection and email security.' ONE hospital is named (Grover C. Dils Medical Center); the other three are identifiable only by county, which is a reading, not a naming. The project describes a service NRHP delivers, the shape §10.2's AHHA negative codes IN_KIND_BENEFIT; no per-hospital split is published and none is imputed (§6.2). PRIOR CODING: IN_KIND_BENEFIT; Curated override: the charitable foundation of Nevada Rural Hospital Partners, the state's rural hospital association -- an association foundation, not a hospital (§10.2). §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds, and the source names hospitals among the parties the funded work serves. These dollars must never enter a 'funds distributed to hospitals' total; they are kept visible rather than discarded.</t>
@@ -19160,7 +19163,7 @@
         <v>125</v>
       </c>
       <c r="V110" t="s">
-        <v>101</v>
+        <v>792</v>
       </c>
       <c r="W110" t="s">
         <v>701</v>
@@ -19181,16 +19184,16 @@
         <v>293</v>
       </c>
       <c r="AC110" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AD110" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AE110" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AF110" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG110" t="s">
         <v>701</v>
@@ -19212,7 +19215,7 @@
         <v>112</v>
       </c>
       <c r="AN110" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO110" t="n">
         <v>19</v>
@@ -19230,7 +19233,7 @@
       <c r="AV110"/>
       <c r="AW110"/>
       <c r="AX110" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AY110" t="s">
         <v>284</v>
@@ -19260,7 +19263,7 @@
         <v>91</v>
       </c>
       <c r="G111" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H111" t="s">
         <v>91</v>
@@ -19319,13 +19322,13 @@
         <v>106</v>
       </c>
       <c r="AD111" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AE111" t="s">
         <v>2</v>
       </c>
       <c r="AF111" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AG111" t="s">
         <v>701</v>
@@ -19365,7 +19368,7 @@
       <c r="AV111"/>
       <c r="AW111"/>
       <c r="AX111" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AY111" t="s">
         <v>463</v>
@@ -19383,7 +19386,7 @@
         <v>111</v>
       </c>
       <c r="C112" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D112" t="n">
         <v>1141440</v>
@@ -19395,7 +19398,7 @@
         <v>93</v>
       </c>
       <c r="G112" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H112" t="s">
         <v>91</v>
@@ -19454,13 +19457,13 @@
         <v>436</v>
       </c>
       <c r="AD112" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AE112" t="s">
         <v>186</v>
       </c>
       <c r="AF112" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AG112" t="s">
         <v>701</v>
@@ -19500,10 +19503,10 @@
       <c r="AV112"/>
       <c r="AW112"/>
       <c r="AX112" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AY112" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AZ112" t="n">
         <v>1141440</v>
@@ -19518,7 +19521,7 @@
         <v>112</v>
       </c>
       <c r="C113" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D113" t="n">
         <v>985700</v>
@@ -19530,7 +19533,7 @@
         <v>91</v>
       </c>
       <c r="G113" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H113" t="s">
         <v>91</v>
@@ -19586,16 +19589,16 @@
       </c>
       <c r="AB113"/>
       <c r="AC113" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AD113" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AE113" t="s">
         <v>219</v>
       </c>
       <c r="AF113" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG113" t="s">
         <v>701</v>
@@ -19637,7 +19640,7 @@
       <c r="AV113"/>
       <c r="AW113"/>
       <c r="AX113" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AY113" t="s">
         <v>569</v>
@@ -19655,7 +19658,7 @@
         <v>113</v>
       </c>
       <c r="C114" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D114" t="n">
         <v>231316</v>
@@ -19667,7 +19670,7 @@
         <v>93</v>
       </c>
       <c r="G114" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H114" t="s">
         <v>91</v>
@@ -19726,13 +19729,13 @@
         <v>436</v>
       </c>
       <c r="AD114" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AE114" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AF114" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG114" t="s">
         <v>701</v>
@@ -19754,7 +19757,7 @@
         <v>112</v>
       </c>
       <c r="AN114" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AO114" t="n">
         <v>23</v>
@@ -19772,10 +19775,10 @@
       <c r="AV114"/>
       <c r="AW114"/>
       <c r="AX114" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AY114" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AZ114" t="n">
         <v>165750</v>
@@ -19790,19 +19793,19 @@
         <v>114</v>
       </c>
       <c r="C115" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D115" t="n">
         <v>4550000</v>
       </c>
       <c r="E115" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F115" t="s">
         <v>93</v>
       </c>
       <c r="G115" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H115" t="s">
         <v>91</v>
@@ -19833,7 +19836,7 @@
       <c r="R115"/>
       <c r="S115"/>
       <c r="T115" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="U115" t="s">
         <v>100</v>
@@ -19858,16 +19861,16 @@
       </c>
       <c r="AB115"/>
       <c r="AC115" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AD115" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AE115" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AF115" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG115" t="s">
         <v>701</v>
@@ -19889,7 +19892,7 @@
         <v>112</v>
       </c>
       <c r="AN115" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AO115" t="n">
         <v>24</v>
@@ -19907,10 +19910,10 @@
       <c r="AV115"/>
       <c r="AW115"/>
       <c r="AX115" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AY115" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AZ115" t="n">
         <v>4550000</v>
@@ -19925,7 +19928,7 @@
         <v>115</v>
       </c>
       <c r="C116" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D116" t="n">
         <v>594715</v>
@@ -19937,7 +19940,7 @@
         <v>93</v>
       </c>
       <c r="G116" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H116" t="s">
         <v>91</v>
@@ -19949,7 +19952,7 @@
         <v>2026</v>
       </c>
       <c r="K116" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L116" t="s">
         <v>95</v>
@@ -19968,7 +19971,7 @@
       <c r="R116"/>
       <c r="S116"/>
       <c r="T116" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U116" t="s">
         <v>100</v>
@@ -19977,7 +19980,7 @@
         <v>101</v>
       </c>
       <c r="W116" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X116" t="s">
         <v>103</v>
@@ -19993,44 +19996,44 @@
       </c>
       <c r="AB116"/>
       <c r="AC116" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD116" t="s">
+        <v>837</v>
+      </c>
+      <c r="AE116" t="s">
+        <v>838</v>
+      </c>
+      <c r="AF116" t="s">
+        <v>839</v>
+      </c>
+      <c r="AG116" t="s">
         <v>835</v>
       </c>
-      <c r="AD116" t="s">
-        <v>836</v>
-      </c>
-      <c r="AE116" t="s">
-        <v>837</v>
-      </c>
-      <c r="AF116" t="s">
-        <v>838</v>
-      </c>
-      <c r="AG116" t="s">
-        <v>834</v>
-      </c>
       <c r="AH116" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI116" t="n">
         <v>36</v>
       </c>
       <c r="AJ116"/>
       <c r="AK116" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL116" t="s">
         <v>840</v>
-      </c>
-      <c r="AL116" t="s">
-        <v>839</v>
       </c>
       <c r="AM116" t="s">
         <v>112</v>
       </c>
       <c r="AN116" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AO116" t="n">
         <v>1</v>
       </c>
       <c r="AP116" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ116" t="s">
         <v>594</v>
@@ -20042,10 +20045,10 @@
       <c r="AV116"/>
       <c r="AW116"/>
       <c r="AX116" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AY116" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AZ116" t="n">
         <v>594715</v>
@@ -20060,7 +20063,7 @@
         <v>116</v>
       </c>
       <c r="C117" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D117" t="n">
         <v>495075</v>
@@ -20072,7 +20075,7 @@
         <v>93</v>
       </c>
       <c r="G117" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H117" t="s">
         <v>91</v>
@@ -20084,7 +20087,7 @@
         <v>2026</v>
       </c>
       <c r="K117" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L117" t="s">
         <v>95</v>
@@ -20112,7 +20115,7 @@
         <v>601</v>
       </c>
       <c r="W117" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X117" t="s">
         <v>103</v>
@@ -20131,41 +20134,41 @@
         <v>436</v>
       </c>
       <c r="AD117" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AE117" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AF117" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AG117" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH117" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI117" t="n">
         <v>36</v>
       </c>
       <c r="AJ117"/>
       <c r="AK117" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL117" t="s">
         <v>840</v>
-      </c>
-      <c r="AL117" t="s">
-        <v>839</v>
       </c>
       <c r="AM117" t="s">
         <v>112</v>
       </c>
       <c r="AN117" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AO117" t="n">
         <v>2</v>
       </c>
       <c r="AP117" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ117" t="s">
         <v>594</v>
@@ -20177,10 +20180,10 @@
       <c r="AV117"/>
       <c r="AW117"/>
       <c r="AX117" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AY117" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AZ117" t="n">
         <v>495075</v>
@@ -20195,7 +20198,7 @@
         <v>117</v>
       </c>
       <c r="C118" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D118" t="n">
         <v>403996</v>
@@ -20207,7 +20210,7 @@
         <v>93</v>
       </c>
       <c r="G118" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H118" t="s">
         <v>91</v>
@@ -20219,7 +20222,7 @@
         <v>2026</v>
       </c>
       <c r="K118" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L118" t="s">
         <v>95</v>
@@ -20247,7 +20250,7 @@
         <v>601</v>
       </c>
       <c r="W118" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X118" t="s">
         <v>103</v>
@@ -20266,41 +20269,41 @@
         <v>436</v>
       </c>
       <c r="AD118" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AE118" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AF118" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG118" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH118" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI118" t="n">
         <v>36</v>
       </c>
       <c r="AJ118"/>
       <c r="AK118" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL118" t="s">
         <v>840</v>
-      </c>
-      <c r="AL118" t="s">
-        <v>839</v>
       </c>
       <c r="AM118" t="s">
         <v>112</v>
       </c>
       <c r="AN118" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AO118" t="n">
         <v>3</v>
       </c>
       <c r="AP118" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ118" t="s">
         <v>594</v>
@@ -20312,10 +20315,10 @@
       <c r="AV118"/>
       <c r="AW118"/>
       <c r="AX118" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AY118" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AZ118" t="n">
         <v>403996</v>
@@ -20330,7 +20333,7 @@
         <v>118</v>
       </c>
       <c r="C119" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D119" t="n">
         <v>458370</v>
@@ -20342,7 +20345,7 @@
         <v>93</v>
       </c>
       <c r="G119" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H119" t="s">
         <v>91</v>
@@ -20354,7 +20357,7 @@
         <v>2026</v>
       </c>
       <c r="K119" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L119" t="s">
         <v>95</v>
@@ -20382,7 +20385,7 @@
         <v>101</v>
       </c>
       <c r="W119" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X119" t="s">
         <v>103</v>
@@ -20401,29 +20404,29 @@
         <v>565</v>
       </c>
       <c r="AD119" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AE119" t="s">
         <v>316</v>
       </c>
       <c r="AF119" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AG119" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH119" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI119" t="n">
         <v>36</v>
       </c>
       <c r="AJ119"/>
       <c r="AK119" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL119" t="s">
         <v>840</v>
-      </c>
-      <c r="AL119" t="s">
-        <v>839</v>
       </c>
       <c r="AM119" t="s">
         <v>112</v>
@@ -20435,7 +20438,7 @@
         <v>4</v>
       </c>
       <c r="AP119" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ119" t="s">
         <v>594</v>
@@ -20447,10 +20450,10 @@
       <c r="AV119"/>
       <c r="AW119"/>
       <c r="AX119" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AY119" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AZ119" t="n">
         <v>458370</v>
@@ -20465,7 +20468,7 @@
         <v>119</v>
       </c>
       <c r="C120" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D120" t="n">
         <v>273950.89</v>
@@ -20477,7 +20480,7 @@
         <v>93</v>
       </c>
       <c r="G120" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H120" t="s">
         <v>91</v>
@@ -20489,7 +20492,7 @@
         <v>2026</v>
       </c>
       <c r="K120" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L120" t="s">
         <v>95</v>
@@ -20517,7 +20520,7 @@
         <v>601</v>
       </c>
       <c r="W120" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X120" t="s">
         <v>103</v>
@@ -20536,41 +20539,41 @@
         <v>436</v>
       </c>
       <c r="AD120" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AE120" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AF120" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AG120" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH120" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI120" t="n">
         <v>36</v>
       </c>
       <c r="AJ120"/>
       <c r="AK120" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL120" t="s">
         <v>840</v>
-      </c>
-      <c r="AL120" t="s">
-        <v>839</v>
       </c>
       <c r="AM120" t="s">
         <v>112</v>
       </c>
       <c r="AN120" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AO120" t="n">
         <v>5</v>
       </c>
       <c r="AP120" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ120" t="s">
         <v>594</v>
@@ -20582,10 +20585,10 @@
       <c r="AV120"/>
       <c r="AW120"/>
       <c r="AX120" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AY120" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AZ120" t="n">
         <v>273950.89</v>
@@ -20612,7 +20615,7 @@
         <v>91</v>
       </c>
       <c r="G121" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H121" t="s">
         <v>91</v>
@@ -20624,7 +20627,7 @@
         <v>2026</v>
       </c>
       <c r="K121" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L121" t="s">
         <v>95</v>
@@ -20652,7 +20655,7 @@
         <v>101</v>
       </c>
       <c r="W121" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X121" t="s">
         <v>103</v>
@@ -20671,29 +20674,29 @@
         <v>106</v>
       </c>
       <c r="AD121" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AE121" t="s">
         <v>202</v>
       </c>
       <c r="AF121" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AG121" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH121" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI121" t="n">
         <v>36</v>
       </c>
       <c r="AJ121"/>
       <c r="AK121" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL121" t="s">
         <v>840</v>
-      </c>
-      <c r="AL121" t="s">
-        <v>839</v>
       </c>
       <c r="AM121" t="s">
         <v>112</v>
@@ -20705,7 +20708,7 @@
         <v>6</v>
       </c>
       <c r="AP121" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ121" t="s">
         <v>594</v>
@@ -20717,7 +20720,7 @@
       <c r="AV121"/>
       <c r="AW121"/>
       <c r="AX121" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AY121" t="s">
         <v>199</v>
@@ -20735,7 +20738,7 @@
         <v>121</v>
       </c>
       <c r="C122" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D122" t="n">
         <v>950668.06</v>
@@ -20747,7 +20750,7 @@
         <v>93</v>
       </c>
       <c r="G122" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H122" t="s">
         <v>91</v>
@@ -20759,7 +20762,7 @@
         <v>2026</v>
       </c>
       <c r="K122" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L122" t="s">
         <v>95</v>
@@ -20778,7 +20781,7 @@
       <c r="R122"/>
       <c r="S122"/>
       <c r="T122" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U122" t="s">
         <v>100</v>
@@ -20787,7 +20790,7 @@
         <v>101</v>
       </c>
       <c r="W122" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X122" t="s">
         <v>103</v>
@@ -20803,32 +20806,32 @@
       </c>
       <c r="AB122"/>
       <c r="AC122" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AD122" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AE122" t="s">
         <v>671</v>
       </c>
       <c r="AF122" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AG122" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH122" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI122" t="n">
         <v>36</v>
       </c>
       <c r="AJ122"/>
       <c r="AK122" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL122" t="s">
         <v>840</v>
-      </c>
-      <c r="AL122" t="s">
-        <v>839</v>
       </c>
       <c r="AM122" t="s">
         <v>112</v>
@@ -20840,7 +20843,7 @@
         <v>7</v>
       </c>
       <c r="AP122" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ122" t="s">
         <v>594</v>
@@ -20852,10 +20855,10 @@
       <c r="AV122"/>
       <c r="AW122"/>
       <c r="AX122" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AY122" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AZ122" t="n">
         <v>523847</v>
@@ -20870,7 +20873,7 @@
         <v>122</v>
       </c>
       <c r="C123" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D123" t="n">
         <v>523807.08</v>
@@ -20882,7 +20885,7 @@
         <v>93</v>
       </c>
       <c r="G123" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H123" t="s">
         <v>91</v>
@@ -20894,7 +20897,7 @@
         <v>2026</v>
       </c>
       <c r="K123" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L123" t="s">
         <v>95</v>
@@ -20922,7 +20925,7 @@
         <v>601</v>
       </c>
       <c r="W123" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X123" t="s">
         <v>103</v>
@@ -20941,41 +20944,41 @@
         <v>436</v>
       </c>
       <c r="AD123" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AE123" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AF123" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AG123" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH123" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI123" t="n">
         <v>36</v>
       </c>
       <c r="AJ123"/>
       <c r="AK123" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL123" t="s">
         <v>840</v>
-      </c>
-      <c r="AL123" t="s">
-        <v>839</v>
       </c>
       <c r="AM123" t="s">
         <v>112</v>
       </c>
       <c r="AN123" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AO123" t="n">
         <v>8</v>
       </c>
       <c r="AP123" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ123" t="s">
         <v>594</v>
@@ -20987,10 +20990,10 @@
       <c r="AV123"/>
       <c r="AW123"/>
       <c r="AX123" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AY123" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AZ123" t="n">
         <v>523847</v>
@@ -21017,7 +21020,7 @@
         <v>91</v>
       </c>
       <c r="G124" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H124" t="s">
         <v>91</v>
@@ -21029,7 +21032,7 @@
         <v>2026</v>
       </c>
       <c r="K124" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L124" t="s">
         <v>95</v>
@@ -21057,7 +21060,7 @@
         <v>101</v>
       </c>
       <c r="W124" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X124" t="s">
         <v>103</v>
@@ -21076,29 +21079,29 @@
         <v>106</v>
       </c>
       <c r="AD124" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AE124" t="s">
         <v>460</v>
       </c>
       <c r="AF124" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="AG124" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH124" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI124" t="n">
         <v>36</v>
       </c>
       <c r="AJ124"/>
       <c r="AK124" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL124" t="s">
         <v>840</v>
-      </c>
-      <c r="AL124" t="s">
-        <v>839</v>
       </c>
       <c r="AM124" t="s">
         <v>112</v>
@@ -21110,7 +21113,7 @@
         <v>9</v>
       </c>
       <c r="AP124" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ124" t="s">
         <v>594</v>
@@ -21122,7 +21125,7 @@
       <c r="AV124"/>
       <c r="AW124"/>
       <c r="AX124" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AY124" t="s">
         <v>457</v>
@@ -21140,7 +21143,7 @@
         <v>124</v>
       </c>
       <c r="C125" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D125" t="n">
         <v>497077</v>
@@ -21152,7 +21155,7 @@
         <v>93</v>
       </c>
       <c r="G125" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H125" t="s">
         <v>91</v>
@@ -21164,7 +21167,7 @@
         <v>2026</v>
       </c>
       <c r="K125" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L125" t="s">
         <v>95</v>
@@ -21192,7 +21195,7 @@
         <v>601</v>
       </c>
       <c r="W125" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X125" t="s">
         <v>103</v>
@@ -21211,41 +21214,41 @@
         <v>436</v>
       </c>
       <c r="AD125" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AE125" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AF125" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AG125" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH125" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI125" t="n">
         <v>36</v>
       </c>
       <c r="AJ125"/>
       <c r="AK125" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL125" t="s">
         <v>840</v>
-      </c>
-      <c r="AL125" t="s">
-        <v>839</v>
       </c>
       <c r="AM125" t="s">
         <v>112</v>
       </c>
       <c r="AN125" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AO125" t="n">
         <v>10</v>
       </c>
       <c r="AP125" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ125" t="s">
         <v>594</v>
@@ -21257,10 +21260,10 @@
       <c r="AV125"/>
       <c r="AW125"/>
       <c r="AX125" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AY125" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AZ125" t="n">
         <v>497077</v>
@@ -21275,7 +21278,7 @@
         <v>125</v>
       </c>
       <c r="C126" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D126" t="n">
         <v>304373</v>
@@ -21287,7 +21290,7 @@
         <v>93</v>
       </c>
       <c r="G126" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H126" t="s">
         <v>91</v>
@@ -21299,7 +21302,7 @@
         <v>2026</v>
       </c>
       <c r="K126" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L126" t="s">
         <v>95</v>
@@ -21318,7 +21321,7 @@
       <c r="R126"/>
       <c r="S126"/>
       <c r="T126" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U126" t="s">
         <v>100</v>
@@ -21327,7 +21330,7 @@
         <v>101</v>
       </c>
       <c r="W126" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X126" t="s">
         <v>103</v>
@@ -21343,44 +21346,44 @@
       </c>
       <c r="AB126"/>
       <c r="AC126" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD126" t="s">
+        <v>895</v>
+      </c>
+      <c r="AE126" t="s">
+        <v>896</v>
+      </c>
+      <c r="AF126" t="s">
+        <v>897</v>
+      </c>
+      <c r="AG126" t="s">
         <v>835</v>
       </c>
-      <c r="AD126" t="s">
-        <v>894</v>
-      </c>
-      <c r="AE126" t="s">
-        <v>895</v>
-      </c>
-      <c r="AF126" t="s">
-        <v>896</v>
-      </c>
-      <c r="AG126" t="s">
-        <v>834</v>
-      </c>
       <c r="AH126" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI126" t="n">
         <v>36</v>
       </c>
       <c r="AJ126"/>
       <c r="AK126" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL126" t="s">
         <v>840</v>
-      </c>
-      <c r="AL126" t="s">
-        <v>839</v>
       </c>
       <c r="AM126" t="s">
         <v>112</v>
       </c>
       <c r="AN126" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AO126" t="n">
         <v>11</v>
       </c>
       <c r="AP126" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ126" t="s">
         <v>594</v>
@@ -21392,10 +21395,10 @@
       <c r="AV126"/>
       <c r="AW126"/>
       <c r="AX126" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AY126" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AZ126" t="n">
         <v>304373</v>
@@ -21410,7 +21413,7 @@
         <v>126</v>
       </c>
       <c r="C127" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D127" t="n">
         <v>139979</v>
@@ -21422,7 +21425,7 @@
         <v>93</v>
       </c>
       <c r="G127" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H127" t="s">
         <v>91</v>
@@ -21434,7 +21437,7 @@
         <v>2026</v>
       </c>
       <c r="K127" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L127" t="s">
         <v>95</v>
@@ -21462,7 +21465,7 @@
         <v>601</v>
       </c>
       <c r="W127" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X127" t="s">
         <v>103</v>
@@ -21481,29 +21484,29 @@
         <v>436</v>
       </c>
       <c r="AD127" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="AE127" t="s">
         <v>186</v>
       </c>
       <c r="AF127" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AG127" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH127" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI127" t="n">
         <v>36</v>
       </c>
       <c r="AJ127"/>
       <c r="AK127" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL127" t="s">
         <v>840</v>
-      </c>
-      <c r="AL127" t="s">
-        <v>839</v>
       </c>
       <c r="AM127" t="s">
         <v>112</v>
@@ -21515,7 +21518,7 @@
         <v>12</v>
       </c>
       <c r="AP127" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ127" t="s">
         <v>594</v>
@@ -21527,10 +21530,10 @@
       <c r="AV127"/>
       <c r="AW127"/>
       <c r="AX127" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="AY127" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="AZ127" t="n">
         <v>142997</v>
@@ -21545,7 +21548,7 @@
         <v>127</v>
       </c>
       <c r="C128" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D128" t="n">
         <v>875334.32</v>
@@ -21557,7 +21560,7 @@
         <v>93</v>
       </c>
       <c r="G128" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H128" t="s">
         <v>91</v>
@@ -21569,7 +21572,7 @@
         <v>2026</v>
       </c>
       <c r="K128" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L128" t="s">
         <v>95</v>
@@ -21597,7 +21600,7 @@
         <v>601</v>
       </c>
       <c r="W128" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X128" t="s">
         <v>103</v>
@@ -21616,41 +21619,41 @@
         <v>436</v>
       </c>
       <c r="AD128" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="AE128" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AF128" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="AG128" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH128" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI128" t="n">
         <v>36</v>
       </c>
       <c r="AJ128"/>
       <c r="AK128" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL128" t="s">
         <v>840</v>
-      </c>
-      <c r="AL128" t="s">
-        <v>839</v>
       </c>
       <c r="AM128" t="s">
         <v>112</v>
       </c>
       <c r="AN128" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AO128" t="n">
         <v>13</v>
       </c>
       <c r="AP128" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ128" t="s">
         <v>594</v>
@@ -21662,10 +21665,10 @@
       <c r="AV128"/>
       <c r="AW128"/>
       <c r="AX128" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AY128" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AZ128" t="n">
         <v>883124</v>
@@ -21692,7 +21695,7 @@
         <v>91</v>
       </c>
       <c r="G129" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H129" t="s">
         <v>91</v>
@@ -21704,7 +21707,7 @@
         <v>2026</v>
       </c>
       <c r="K129" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L129" t="s">
         <v>95</v>
@@ -21734,7 +21737,7 @@
         <v>101</v>
       </c>
       <c r="W129" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X129" t="s">
         <v>103</v>
@@ -21750,44 +21753,44 @@
       </c>
       <c r="AB129"/>
       <c r="AC129" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AD129" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="AE129" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AF129" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AG129" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH129" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI129" t="n">
         <v>36</v>
       </c>
       <c r="AJ129"/>
       <c r="AK129" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL129" t="s">
         <v>840</v>
-      </c>
-      <c r="AL129" t="s">
-        <v>839</v>
       </c>
       <c r="AM129" t="s">
         <v>112</v>
       </c>
       <c r="AN129" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AO129" t="n">
         <v>14</v>
       </c>
       <c r="AP129" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ129" t="s">
         <v>594</v>
@@ -21799,13 +21802,13 @@
       <c r="AT129"/>
       <c r="AU129"/>
       <c r="AV129" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AW129" t="s">
         <v>614</v>
       </c>
       <c r="AX129" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AY129" t="s">
         <v>388</v>
@@ -21823,7 +21826,7 @@
         <v>129</v>
       </c>
       <c r="C130" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D130" t="n">
         <v>500000</v>
@@ -21835,7 +21838,7 @@
         <v>93</v>
       </c>
       <c r="G130" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H130" t="s">
         <v>91</v>
@@ -21847,7 +21850,7 @@
         <v>2026</v>
       </c>
       <c r="K130" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L130" t="s">
         <v>95</v>
@@ -21866,7 +21869,7 @@
       <c r="R130"/>
       <c r="S130"/>
       <c r="T130" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U130" t="s">
         <v>100</v>
@@ -21875,7 +21878,7 @@
         <v>101</v>
       </c>
       <c r="W130" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X130" t="s">
         <v>103</v>
@@ -21891,44 +21894,44 @@
       </c>
       <c r="AB130"/>
       <c r="AC130" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD130" t="s">
+        <v>919</v>
+      </c>
+      <c r="AE130" t="s">
+        <v>920</v>
+      </c>
+      <c r="AF130" t="s">
+        <v>921</v>
+      </c>
+      <c r="AG130" t="s">
         <v>835</v>
       </c>
-      <c r="AD130" t="s">
-        <v>918</v>
-      </c>
-      <c r="AE130" t="s">
-        <v>919</v>
-      </c>
-      <c r="AF130" t="s">
-        <v>920</v>
-      </c>
-      <c r="AG130" t="s">
-        <v>834</v>
-      </c>
       <c r="AH130" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI130" t="n">
         <v>36</v>
       </c>
       <c r="AJ130"/>
       <c r="AK130" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL130" t="s">
         <v>840</v>
-      </c>
-      <c r="AL130" t="s">
-        <v>839</v>
       </c>
       <c r="AM130" t="s">
         <v>112</v>
       </c>
       <c r="AN130" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AO130" t="n">
         <v>15</v>
       </c>
       <c r="AP130" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ130" t="s">
         <v>594</v>
@@ -21940,10 +21943,10 @@
       <c r="AV130"/>
       <c r="AW130"/>
       <c r="AX130" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="AY130" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AZ130" t="n">
         <v>670554</v>
@@ -21958,7 +21961,7 @@
         <v>130</v>
       </c>
       <c r="C131" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D131" t="n">
         <v>912521</v>
@@ -21970,7 +21973,7 @@
         <v>93</v>
       </c>
       <c r="G131" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H131" t="s">
         <v>91</v>
@@ -21982,7 +21985,7 @@
         <v>2026</v>
       </c>
       <c r="K131" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L131" t="s">
         <v>95</v>
@@ -22010,7 +22013,7 @@
         <v>101</v>
       </c>
       <c r="W131" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X131" t="s">
         <v>103</v>
@@ -22029,41 +22032,41 @@
         <v>525</v>
       </c>
       <c r="AD131" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AE131" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AF131" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="AG131" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH131" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI131" t="n">
         <v>36</v>
       </c>
       <c r="AJ131"/>
       <c r="AK131" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL131" t="s">
         <v>840</v>
-      </c>
-      <c r="AL131" t="s">
-        <v>839</v>
       </c>
       <c r="AM131" t="s">
         <v>112</v>
       </c>
       <c r="AN131" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AO131" t="n">
         <v>16</v>
       </c>
       <c r="AP131" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ131" t="s">
         <v>594</v>
@@ -22075,10 +22078,10 @@
       <c r="AV131"/>
       <c r="AW131"/>
       <c r="AX131" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="AY131" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="AZ131" t="n">
         <v>931934</v>
@@ -22093,7 +22096,7 @@
         <v>131</v>
       </c>
       <c r="C132" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D132" t="n">
         <v>437843.58</v>
@@ -22105,7 +22108,7 @@
         <v>93</v>
       </c>
       <c r="G132" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H132" t="s">
         <v>91</v>
@@ -22117,7 +22120,7 @@
         <v>2026</v>
       </c>
       <c r="K132" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L132" t="s">
         <v>95</v>
@@ -22136,7 +22139,7 @@
       <c r="R132"/>
       <c r="S132"/>
       <c r="T132" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U132" t="s">
         <v>100</v>
@@ -22145,7 +22148,7 @@
         <v>101</v>
       </c>
       <c r="W132" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X132" t="s">
         <v>103</v>
@@ -22161,44 +22164,44 @@
       </c>
       <c r="AB132"/>
       <c r="AC132" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD132" t="s">
+        <v>931</v>
+      </c>
+      <c r="AE132" t="s">
+        <v>932</v>
+      </c>
+      <c r="AF132" t="s">
+        <v>933</v>
+      </c>
+      <c r="AG132" t="s">
         <v>835</v>
       </c>
-      <c r="AD132" t="s">
-        <v>930</v>
-      </c>
-      <c r="AE132" t="s">
-        <v>931</v>
-      </c>
-      <c r="AF132" t="s">
-        <v>932</v>
-      </c>
-      <c r="AG132" t="s">
-        <v>834</v>
-      </c>
       <c r="AH132" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI132" t="n">
         <v>36</v>
       </c>
       <c r="AJ132"/>
       <c r="AK132" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL132" t="s">
         <v>840</v>
-      </c>
-      <c r="AL132" t="s">
-        <v>839</v>
       </c>
       <c r="AM132" t="s">
         <v>112</v>
       </c>
       <c r="AN132" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AO132" t="n">
         <v>17</v>
       </c>
       <c r="AP132" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ132" t="s">
         <v>594</v>
@@ -22210,10 +22213,10 @@
       <c r="AV132"/>
       <c r="AW132"/>
       <c r="AX132" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="AY132" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AZ132" t="n">
         <v>437844</v>
@@ -22228,7 +22231,7 @@
         <v>132</v>
       </c>
       <c r="C133" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D133" t="n">
         <v>423299.3</v>
@@ -22240,7 +22243,7 @@
         <v>93</v>
       </c>
       <c r="G133" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H133" t="s">
         <v>91</v>
@@ -22252,7 +22255,7 @@
         <v>2026</v>
       </c>
       <c r="K133" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L133" t="s">
         <v>95</v>
@@ -22271,7 +22274,7 @@
       <c r="R133"/>
       <c r="S133"/>
       <c r="T133" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U133" t="s">
         <v>100</v>
@@ -22280,7 +22283,7 @@
         <v>101</v>
       </c>
       <c r="W133" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X133" t="s">
         <v>103</v>
@@ -22296,32 +22299,32 @@
       </c>
       <c r="AB133"/>
       <c r="AC133" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AD133" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AE133" t="s">
         <v>671</v>
       </c>
       <c r="AF133" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AG133" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH133" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI133" t="n">
         <v>36</v>
       </c>
       <c r="AJ133"/>
       <c r="AK133" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL133" t="s">
         <v>840</v>
-      </c>
-      <c r="AL133" t="s">
-        <v>839</v>
       </c>
       <c r="AM133" t="s">
         <v>112</v>
@@ -22333,7 +22336,7 @@
         <v>18</v>
       </c>
       <c r="AP133" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ133" t="s">
         <v>594</v>
@@ -22345,10 +22348,10 @@
       <c r="AV133"/>
       <c r="AW133"/>
       <c r="AX133" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AY133" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="AZ133" t="n">
         <v>470468</v>
@@ -22363,7 +22366,7 @@
         <v>133</v>
       </c>
       <c r="C134" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D134" t="n">
         <v>463542</v>
@@ -22375,7 +22378,7 @@
         <v>93</v>
       </c>
       <c r="G134" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H134" t="s">
         <v>91</v>
@@ -22387,7 +22390,7 @@
         <v>2026</v>
       </c>
       <c r="K134" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L134" t="s">
         <v>95</v>
@@ -22406,7 +22409,7 @@
       <c r="R134"/>
       <c r="S134"/>
       <c r="T134" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U134" t="s">
         <v>100</v>
@@ -22415,7 +22418,7 @@
         <v>101</v>
       </c>
       <c r="W134" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X134" t="s">
         <v>103</v>
@@ -22431,44 +22434,44 @@
       </c>
       <c r="AB134"/>
       <c r="AC134" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD134" t="s">
+        <v>941</v>
+      </c>
+      <c r="AE134" t="s">
+        <v>942</v>
+      </c>
+      <c r="AF134" t="s">
+        <v>943</v>
+      </c>
+      <c r="AG134" t="s">
         <v>835</v>
       </c>
-      <c r="AD134" t="s">
-        <v>940</v>
-      </c>
-      <c r="AE134" t="s">
-        <v>941</v>
-      </c>
-      <c r="AF134" t="s">
-        <v>942</v>
-      </c>
-      <c r="AG134" t="s">
-        <v>834</v>
-      </c>
       <c r="AH134" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI134" t="n">
         <v>36</v>
       </c>
       <c r="AJ134"/>
       <c r="AK134" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL134" t="s">
         <v>840</v>
-      </c>
-      <c r="AL134" t="s">
-        <v>839</v>
       </c>
       <c r="AM134" t="s">
         <v>112</v>
       </c>
       <c r="AN134" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="AO134" t="n">
         <v>19</v>
       </c>
       <c r="AP134" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ134" t="s">
         <v>594</v>
@@ -22480,10 +22483,10 @@
       <c r="AV134"/>
       <c r="AW134"/>
       <c r="AX134" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="AY134" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AZ134" t="n">
         <v>463542</v>
@@ -22498,7 +22501,7 @@
         <v>134</v>
       </c>
       <c r="C135" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D135" t="n">
         <v>185885.27</v>
@@ -22510,7 +22513,7 @@
         <v>93</v>
       </c>
       <c r="G135" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H135" t="s">
         <v>91</v>
@@ -22522,7 +22525,7 @@
         <v>2026</v>
       </c>
       <c r="K135" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L135" t="s">
         <v>95</v>
@@ -22541,7 +22544,7 @@
       <c r="R135"/>
       <c r="S135"/>
       <c r="T135" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U135" t="s">
         <v>100</v>
@@ -22550,7 +22553,7 @@
         <v>101</v>
       </c>
       <c r="W135" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X135" t="s">
         <v>103</v>
@@ -22566,32 +22569,32 @@
       </c>
       <c r="AB135"/>
       <c r="AC135" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AD135" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AE135" t="s">
         <v>186</v>
       </c>
       <c r="AF135" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="AG135" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH135" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI135" t="n">
         <v>36</v>
       </c>
       <c r="AJ135"/>
       <c r="AK135" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL135" t="s">
         <v>840</v>
-      </c>
-      <c r="AL135" t="s">
-        <v>839</v>
       </c>
       <c r="AM135" t="s">
         <v>112</v>
@@ -22603,7 +22606,7 @@
         <v>20</v>
       </c>
       <c r="AP135" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ135" t="s">
         <v>594</v>
@@ -22615,10 +22618,10 @@
       <c r="AV135"/>
       <c r="AW135"/>
       <c r="AX135" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="AY135" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AZ135" t="n">
         <v>187888</v>
@@ -22633,7 +22636,7 @@
         <v>135</v>
       </c>
       <c r="C136" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D136" t="n">
         <v>472896.49</v>
@@ -22645,7 +22648,7 @@
         <v>93</v>
       </c>
       <c r="G136" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H136" t="s">
         <v>91</v>
@@ -22657,7 +22660,7 @@
         <v>2026</v>
       </c>
       <c r="K136" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L136" t="s">
         <v>95</v>
@@ -22676,7 +22679,7 @@
       <c r="R136"/>
       <c r="S136"/>
       <c r="T136" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U136" t="s">
         <v>100</v>
@@ -22685,7 +22688,7 @@
         <v>101</v>
       </c>
       <c r="W136" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X136" t="s">
         <v>103</v>
@@ -22701,32 +22704,32 @@
       </c>
       <c r="AB136"/>
       <c r="AC136" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AD136" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AE136" t="s">
         <v>130</v>
       </c>
       <c r="AF136" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AG136" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH136" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI136" t="n">
         <v>36</v>
       </c>
       <c r="AJ136"/>
       <c r="AK136" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL136" t="s">
         <v>840</v>
-      </c>
-      <c r="AL136" t="s">
-        <v>839</v>
       </c>
       <c r="AM136" t="s">
         <v>112</v>
@@ -22738,7 +22741,7 @@
         <v>21</v>
       </c>
       <c r="AP136" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ136" t="s">
         <v>594</v>
@@ -22750,10 +22753,10 @@
       <c r="AV136"/>
       <c r="AW136"/>
       <c r="AX136" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="AY136" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AZ136" t="n">
         <v>472896</v>
@@ -22768,7 +22771,7 @@
         <v>136</v>
       </c>
       <c r="C137" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D137" t="n">
         <v>1402234.53</v>
@@ -22780,7 +22783,7 @@
         <v>93</v>
       </c>
       <c r="G137" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H137" t="s">
         <v>91</v>
@@ -22792,7 +22795,7 @@
         <v>2026</v>
       </c>
       <c r="K137" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L137" t="s">
         <v>95</v>
@@ -22811,7 +22814,7 @@
       <c r="R137"/>
       <c r="S137"/>
       <c r="T137" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U137" t="s">
         <v>100</v>
@@ -22820,7 +22823,7 @@
         <v>101</v>
       </c>
       <c r="W137" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X137" t="s">
         <v>103</v>
@@ -22836,44 +22839,44 @@
       </c>
       <c r="AB137"/>
       <c r="AC137" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD137" t="s">
+        <v>955</v>
+      </c>
+      <c r="AE137" t="s">
+        <v>956</v>
+      </c>
+      <c r="AF137" t="s">
+        <v>957</v>
+      </c>
+      <c r="AG137" t="s">
         <v>835</v>
       </c>
-      <c r="AD137" t="s">
-        <v>954</v>
-      </c>
-      <c r="AE137" t="s">
-        <v>955</v>
-      </c>
-      <c r="AF137" t="s">
-        <v>956</v>
-      </c>
-      <c r="AG137" t="s">
-        <v>834</v>
-      </c>
       <c r="AH137" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI137" t="n">
         <v>36</v>
       </c>
       <c r="AJ137"/>
       <c r="AK137" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL137" t="s">
         <v>840</v>
-      </c>
-      <c r="AL137" t="s">
-        <v>839</v>
       </c>
       <c r="AM137" t="s">
         <v>112</v>
       </c>
       <c r="AN137" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AO137" t="n">
         <v>22</v>
       </c>
       <c r="AP137" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ137" t="s">
         <v>594</v>
@@ -22885,10 +22888,10 @@
       <c r="AV137"/>
       <c r="AW137"/>
       <c r="AX137" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AY137" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AZ137" t="n">
         <v>1402294</v>
@@ -22903,7 +22906,7 @@
         <v>137</v>
       </c>
       <c r="C138" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D138" t="n">
         <v>1478408.1</v>
@@ -22915,7 +22918,7 @@
         <v>93</v>
       </c>
       <c r="G138" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H138" t="s">
         <v>91</v>
@@ -22927,7 +22930,7 @@
         <v>2026</v>
       </c>
       <c r="K138" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L138" t="s">
         <v>95</v>
@@ -22946,7 +22949,7 @@
       <c r="R138"/>
       <c r="S138"/>
       <c r="T138" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U138" t="s">
         <v>100</v>
@@ -22955,7 +22958,7 @@
         <v>101</v>
       </c>
       <c r="W138" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X138" t="s">
         <v>103</v>
@@ -22971,44 +22974,44 @@
       </c>
       <c r="AB138"/>
       <c r="AC138" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD138" t="s">
+        <v>961</v>
+      </c>
+      <c r="AE138" t="s">
+        <v>962</v>
+      </c>
+      <c r="AF138" t="s">
+        <v>963</v>
+      </c>
+      <c r="AG138" t="s">
         <v>835</v>
       </c>
-      <c r="AD138" t="s">
-        <v>960</v>
-      </c>
-      <c r="AE138" t="s">
-        <v>961</v>
-      </c>
-      <c r="AF138" t="s">
-        <v>962</v>
-      </c>
-      <c r="AG138" t="s">
-        <v>834</v>
-      </c>
       <c r="AH138" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI138" t="n">
         <v>36</v>
       </c>
       <c r="AJ138"/>
       <c r="AK138" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL138" t="s">
         <v>840</v>
-      </c>
-      <c r="AL138" t="s">
-        <v>839</v>
       </c>
       <c r="AM138" t="s">
         <v>112</v>
       </c>
       <c r="AN138" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AO138" t="n">
         <v>23</v>
       </c>
       <c r="AP138" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ138" t="s">
         <v>594</v>
@@ -23020,10 +23023,10 @@
       <c r="AV138"/>
       <c r="AW138"/>
       <c r="AX138" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AY138" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AZ138" t="n">
         <v>1502819</v>
@@ -23038,7 +23041,7 @@
         <v>138</v>
       </c>
       <c r="C139" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D139" t="n">
         <v>189198.17</v>
@@ -23050,7 +23053,7 @@
         <v>93</v>
       </c>
       <c r="G139" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H139" t="s">
         <v>91</v>
@@ -23062,7 +23065,7 @@
         <v>2026</v>
       </c>
       <c r="K139" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L139" t="s">
         <v>95</v>
@@ -23090,7 +23093,7 @@
         <v>101</v>
       </c>
       <c r="W139" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X139" t="s">
         <v>103</v>
@@ -23109,41 +23112,41 @@
         <v>175</v>
       </c>
       <c r="AD139" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AE139" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AF139" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AG139" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH139" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI139" t="n">
         <v>36</v>
       </c>
       <c r="AJ139"/>
       <c r="AK139" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL139" t="s">
         <v>840</v>
-      </c>
-      <c r="AL139" t="s">
-        <v>839</v>
       </c>
       <c r="AM139" t="s">
         <v>112</v>
       </c>
       <c r="AN139" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AO139" t="n">
         <v>24</v>
       </c>
       <c r="AP139" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ139" t="s">
         <v>594</v>
@@ -23155,10 +23158,10 @@
       <c r="AV139"/>
       <c r="AW139"/>
       <c r="AX139" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AY139" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="AZ139" t="n">
         <v>227195</v>
@@ -23173,7 +23176,7 @@
         <v>139</v>
       </c>
       <c r="C140" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D140" t="n">
         <v>1370314</v>
@@ -23185,7 +23188,7 @@
         <v>93</v>
       </c>
       <c r="G140" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H140" t="s">
         <v>91</v>
@@ -23197,7 +23200,7 @@
         <v>2026</v>
       </c>
       <c r="K140" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L140" t="s">
         <v>95</v>
@@ -23216,7 +23219,7 @@
       <c r="R140"/>
       <c r="S140"/>
       <c r="T140" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="U140" t="s">
         <v>100</v>
@@ -23225,7 +23228,7 @@
         <v>101</v>
       </c>
       <c r="W140" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X140" t="s">
         <v>103</v>
@@ -23241,44 +23244,44 @@
       </c>
       <c r="AB140"/>
       <c r="AC140" t="s">
+        <v>836</v>
+      </c>
+      <c r="AD140" t="s">
+        <v>974</v>
+      </c>
+      <c r="AE140" t="s">
+        <v>975</v>
+      </c>
+      <c r="AF140" t="s">
+        <v>976</v>
+      </c>
+      <c r="AG140" t="s">
         <v>835</v>
       </c>
-      <c r="AD140" t="s">
-        <v>973</v>
-      </c>
-      <c r="AE140" t="s">
-        <v>974</v>
-      </c>
-      <c r="AF140" t="s">
-        <v>975</v>
-      </c>
-      <c r="AG140" t="s">
-        <v>834</v>
-      </c>
       <c r="AH140" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI140" t="n">
         <v>36</v>
       </c>
       <c r="AJ140"/>
       <c r="AK140" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL140" t="s">
         <v>840</v>
-      </c>
-      <c r="AL140" t="s">
-        <v>839</v>
       </c>
       <c r="AM140" t="s">
         <v>112</v>
       </c>
       <c r="AN140" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AO140" t="n">
         <v>25</v>
       </c>
       <c r="AP140" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ140" t="s">
         <v>594</v>
@@ -23290,10 +23293,10 @@
       <c r="AV140"/>
       <c r="AW140"/>
       <c r="AX140" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AY140" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AZ140" t="n">
         <v>1422055</v>
@@ -23320,7 +23323,7 @@
         <v>91</v>
       </c>
       <c r="G141" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H141" t="s">
         <v>91</v>
@@ -23332,7 +23335,7 @@
         <v>2026</v>
       </c>
       <c r="K141" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L141" t="s">
         <v>95</v>
@@ -23360,7 +23363,7 @@
         <v>101</v>
       </c>
       <c r="W141" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X141" t="s">
         <v>103</v>
@@ -23379,41 +23382,41 @@
         <v>106</v>
       </c>
       <c r="AD141" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AE141" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AF141" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AG141" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH141" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI141" t="n">
         <v>36</v>
       </c>
       <c r="AJ141"/>
       <c r="AK141" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL141" t="s">
         <v>840</v>
-      </c>
-      <c r="AL141" t="s">
-        <v>839</v>
       </c>
       <c r="AM141" t="s">
         <v>112</v>
       </c>
       <c r="AN141" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AO141" t="n">
         <v>26</v>
       </c>
       <c r="AP141" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ141" t="s">
         <v>594</v>
@@ -23425,7 +23428,7 @@
       <c r="AV141"/>
       <c r="AW141"/>
       <c r="AX141" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AY141" t="s">
         <v>235</v>
@@ -23443,7 +23446,7 @@
         <v>141</v>
       </c>
       <c r="C142" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D142" t="n">
         <v>500000</v>
@@ -23455,7 +23458,7 @@
         <v>93</v>
       </c>
       <c r="G142" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H142" t="s">
         <v>91</v>
@@ -23467,7 +23470,7 @@
         <v>2026</v>
       </c>
       <c r="K142" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L142" t="s">
         <v>95</v>
@@ -23495,7 +23498,7 @@
         <v>601</v>
       </c>
       <c r="W142" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X142" t="s">
         <v>103</v>
@@ -23514,41 +23517,41 @@
         <v>436</v>
       </c>
       <c r="AD142" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AE142" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="AF142" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="AG142" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH142" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI142" t="n">
         <v>36</v>
       </c>
       <c r="AJ142"/>
       <c r="AK142" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL142" t="s">
         <v>840</v>
-      </c>
-      <c r="AL142" t="s">
-        <v>839</v>
       </c>
       <c r="AM142" t="s">
         <v>112</v>
       </c>
       <c r="AN142" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="AO142" t="n">
         <v>27</v>
       </c>
       <c r="AP142" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ142" t="s">
         <v>594</v>
@@ -23560,10 +23563,10 @@
       <c r="AV142"/>
       <c r="AW142"/>
       <c r="AX142" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AY142" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="AZ142" t="n">
         <v>500000</v>
@@ -23578,7 +23581,7 @@
         <v>142</v>
       </c>
       <c r="C143" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D143" t="n">
         <v>449999.48</v>
@@ -23590,7 +23593,7 @@
         <v>93</v>
       </c>
       <c r="G143" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H143" t="s">
         <v>91</v>
@@ -23602,7 +23605,7 @@
         <v>2026</v>
       </c>
       <c r="K143" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L143" t="s">
         <v>95</v>
@@ -23630,7 +23633,7 @@
         <v>601</v>
       </c>
       <c r="W143" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X143" t="s">
         <v>103</v>
@@ -23649,41 +23652,41 @@
         <v>436</v>
       </c>
       <c r="AD143" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="AE143" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="AF143" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AG143" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH143" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI143" t="n">
         <v>36</v>
       </c>
       <c r="AJ143"/>
       <c r="AK143" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL143" t="s">
         <v>840</v>
-      </c>
-      <c r="AL143" t="s">
-        <v>839</v>
       </c>
       <c r="AM143" t="s">
         <v>112</v>
       </c>
       <c r="AN143" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="AO143" t="n">
         <v>28</v>
       </c>
       <c r="AP143" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ143" t="s">
         <v>594</v>
@@ -23695,10 +23698,10 @@
       <c r="AV143"/>
       <c r="AW143"/>
       <c r="AX143" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="AY143" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="AZ143" t="n">
         <v>450000</v>
@@ -23713,7 +23716,7 @@
         <v>143</v>
       </c>
       <c r="C144" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D144" t="n">
         <v>3772261</v>
@@ -23725,7 +23728,7 @@
         <v>91</v>
       </c>
       <c r="G144" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H144" t="s">
         <v>91</v>
@@ -23737,7 +23740,7 @@
         <v>2026</v>
       </c>
       <c r="K144" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L144" t="s">
         <v>95</v>
@@ -23756,16 +23759,16 @@
       <c r="R144"/>
       <c r="S144"/>
       <c r="T144" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="U144" t="s">
         <v>125</v>
       </c>
       <c r="V144" t="s">
-        <v>101</v>
+        <v>792</v>
       </c>
       <c r="W144" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X144" t="s">
         <v>103</v>
@@ -23780,47 +23783,47 @@
         <v>292</v>
       </c>
       <c r="AB144" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="AC144" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="AD144" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="AE144" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="AF144" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AG144" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH144" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI144" t="n">
         <v>36</v>
       </c>
       <c r="AJ144"/>
       <c r="AK144" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL144" t="s">
         <v>840</v>
-      </c>
-      <c r="AL144" t="s">
-        <v>839</v>
       </c>
       <c r="AM144" t="s">
         <v>112</v>
       </c>
       <c r="AN144" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="AO144" t="n">
         <v>29</v>
       </c>
       <c r="AP144" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ144" t="s">
         <v>594</v>
@@ -23832,10 +23835,10 @@
       <c r="AV144"/>
       <c r="AW144"/>
       <c r="AX144" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="AY144" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="AZ144" t="n">
         <v>3772261</v>
@@ -23862,7 +23865,7 @@
         <v>93</v>
       </c>
       <c r="G145" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H145" t="s">
         <v>91</v>
@@ -23874,7 +23877,7 @@
         <v>2026</v>
       </c>
       <c r="K145" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L145" t="s">
         <v>95</v>
@@ -23902,7 +23905,7 @@
         <v>601</v>
       </c>
       <c r="W145" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X145" t="s">
         <v>103</v>
@@ -23921,29 +23924,29 @@
         <v>436</v>
       </c>
       <c r="AD145" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="AE145" t="s">
         <v>779</v>
       </c>
       <c r="AF145" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="AG145" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH145" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI145" t="n">
         <v>36</v>
       </c>
       <c r="AJ145"/>
       <c r="AK145" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL145" t="s">
         <v>840</v>
-      </c>
-      <c r="AL145" t="s">
-        <v>839</v>
       </c>
       <c r="AM145" t="s">
         <v>112</v>
@@ -23955,7 +23958,7 @@
         <v>30</v>
       </c>
       <c r="AP145" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ145" t="s">
         <v>594</v>
@@ -23967,7 +23970,7 @@
       <c r="AV145"/>
       <c r="AW145"/>
       <c r="AX145" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="AY145" t="s">
         <v>259</v>
@@ -23997,7 +24000,7 @@
         <v>93</v>
       </c>
       <c r="G146" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H146" t="s">
         <v>91</v>
@@ -24009,7 +24012,7 @@
         <v>2026</v>
       </c>
       <c r="K146" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L146" t="s">
         <v>95</v>
@@ -24037,7 +24040,7 @@
         <v>601</v>
       </c>
       <c r="W146" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X146" t="s">
         <v>103</v>
@@ -24056,41 +24059,41 @@
         <v>436</v>
       </c>
       <c r="AD146" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="AE146" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="AF146" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="AG146" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH146" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI146" t="n">
         <v>36</v>
       </c>
       <c r="AJ146"/>
       <c r="AK146" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL146" t="s">
         <v>840</v>
-      </c>
-      <c r="AL146" t="s">
-        <v>839</v>
       </c>
       <c r="AM146" t="s">
         <v>112</v>
       </c>
       <c r="AN146" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="AO146" t="n">
         <v>31</v>
       </c>
       <c r="AP146" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ146" t="s">
         <v>594</v>
@@ -24102,7 +24105,7 @@
       <c r="AV146"/>
       <c r="AW146"/>
       <c r="AX146" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="AY146" t="s">
         <v>338</v>
@@ -24120,7 +24123,7 @@
         <v>146</v>
       </c>
       <c r="C147" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D147" t="n">
         <v>425000</v>
@@ -24132,7 +24135,7 @@
         <v>93</v>
       </c>
       <c r="G147" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H147" t="s">
         <v>91</v>
@@ -24144,7 +24147,7 @@
         <v>2026</v>
       </c>
       <c r="K147" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L147" t="s">
         <v>95</v>
@@ -24172,7 +24175,7 @@
         <v>601</v>
       </c>
       <c r="W147" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X147" t="s">
         <v>103</v>
@@ -24191,41 +24194,41 @@
         <v>436</v>
       </c>
       <c r="AD147" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="AE147" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="AF147" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="AG147" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH147" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI147" t="n">
         <v>36</v>
       </c>
       <c r="AJ147"/>
       <c r="AK147" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL147" t="s">
         <v>840</v>
-      </c>
-      <c r="AL147" t="s">
-        <v>839</v>
       </c>
       <c r="AM147" t="s">
         <v>112</v>
       </c>
       <c r="AN147" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="AO147" t="n">
         <v>32</v>
       </c>
       <c r="AP147" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ147" t="s">
         <v>594</v>
@@ -24237,10 +24240,10 @@
       <c r="AV147"/>
       <c r="AW147"/>
       <c r="AX147" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="AY147" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="AZ147" t="n">
         <v>425000</v>
@@ -24255,7 +24258,7 @@
         <v>147</v>
       </c>
       <c r="C148" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D148" t="n">
         <v>249312.5</v>
@@ -24267,7 +24270,7 @@
         <v>93</v>
       </c>
       <c r="G148" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H148" t="s">
         <v>91</v>
@@ -24279,7 +24282,7 @@
         <v>2026</v>
       </c>
       <c r="K148" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L148" t="s">
         <v>95</v>
@@ -24307,7 +24310,7 @@
         <v>601</v>
       </c>
       <c r="W148" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X148" t="s">
         <v>103</v>
@@ -24326,41 +24329,41 @@
         <v>436</v>
       </c>
       <c r="AD148" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AE148" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AF148" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="AG148" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH148" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI148" t="n">
         <v>36</v>
       </c>
       <c r="AJ148"/>
       <c r="AK148" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL148" t="s">
         <v>840</v>
-      </c>
-      <c r="AL148" t="s">
-        <v>839</v>
       </c>
       <c r="AM148" t="s">
         <v>112</v>
       </c>
       <c r="AN148" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AO148" t="n">
         <v>33</v>
       </c>
       <c r="AP148" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ148" t="s">
         <v>594</v>
@@ -24372,10 +24375,10 @@
       <c r="AV148"/>
       <c r="AW148"/>
       <c r="AX148" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="AY148" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AZ148" t="n">
         <v>249093</v>
@@ -24390,7 +24393,7 @@
         <v>148</v>
       </c>
       <c r="C149" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D149" t="n">
         <v>495338</v>
@@ -24402,7 +24405,7 @@
         <v>93</v>
       </c>
       <c r="G149" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H149" t="s">
         <v>91</v>
@@ -24414,7 +24417,7 @@
         <v>2026</v>
       </c>
       <c r="K149" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L149" t="s">
         <v>95</v>
@@ -24442,7 +24445,7 @@
         <v>601</v>
       </c>
       <c r="W149" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X149" t="s">
         <v>103</v>
@@ -24461,29 +24464,29 @@
         <v>436</v>
       </c>
       <c r="AD149" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AE149" t="s">
         <v>130</v>
       </c>
       <c r="AF149" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="AG149" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH149" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI149" t="n">
         <v>36</v>
       </c>
       <c r="AJ149"/>
       <c r="AK149" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL149" t="s">
         <v>840</v>
-      </c>
-      <c r="AL149" t="s">
-        <v>839</v>
       </c>
       <c r="AM149" t="s">
         <v>112</v>
@@ -24495,7 +24498,7 @@
         <v>34</v>
       </c>
       <c r="AP149" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ149" t="s">
         <v>594</v>
@@ -24507,10 +24510,10 @@
       <c r="AV149"/>
       <c r="AW149"/>
       <c r="AX149" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="AY149" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="AZ149" t="n">
         <v>497053</v>
@@ -24525,7 +24528,7 @@
         <v>149</v>
       </c>
       <c r="C150" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D150" t="n">
         <v>1690557.34</v>
@@ -24537,7 +24540,7 @@
         <v>93</v>
       </c>
       <c r="G150" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H150" t="s">
         <v>91</v>
@@ -24549,7 +24552,7 @@
         <v>2026</v>
       </c>
       <c r="K150" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L150" t="s">
         <v>95</v>
@@ -24577,7 +24580,7 @@
         <v>101</v>
       </c>
       <c r="W150" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X150" t="s">
         <v>103</v>
@@ -24596,41 +24599,41 @@
         <v>175</v>
       </c>
       <c r="AD150" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="AE150" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="AF150" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="AG150" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH150" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI150" t="n">
         <v>36</v>
       </c>
       <c r="AJ150"/>
       <c r="AK150" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL150" t="s">
         <v>840</v>
-      </c>
-      <c r="AL150" t="s">
-        <v>839</v>
       </c>
       <c r="AM150" t="s">
         <v>112</v>
       </c>
       <c r="AN150" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="AO150" t="n">
         <v>35</v>
       </c>
       <c r="AP150" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ150" t="s">
         <v>594</v>
@@ -24642,10 +24645,10 @@
       <c r="AV150"/>
       <c r="AW150"/>
       <c r="AX150" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="AY150" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="AZ150" t="n">
         <v>1648629</v>
@@ -24660,19 +24663,19 @@
         <v>150</v>
       </c>
       <c r="C151" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D151" t="n">
         <v>550142</v>
       </c>
       <c r="E151" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F151" t="s">
         <v>93</v>
       </c>
       <c r="G151" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H151" t="s">
         <v>91</v>
@@ -24684,7 +24687,7 @@
         <v>2026</v>
       </c>
       <c r="K151" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L151" t="s">
         <v>95</v>
@@ -24703,7 +24706,7 @@
       <c r="R151"/>
       <c r="S151"/>
       <c r="T151" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="U151" t="s">
         <v>100</v>
@@ -24712,7 +24715,7 @@
         <v>101</v>
       </c>
       <c r="W151" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X151" t="s">
         <v>103</v>
@@ -24728,44 +24731,44 @@
       </c>
       <c r="AB151"/>
       <c r="AC151" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AD151" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AE151" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AF151" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="AG151" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AH151" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AI151" t="n">
         <v>36</v>
       </c>
       <c r="AJ151"/>
       <c r="AK151" t="s">
+        <v>841</v>
+      </c>
+      <c r="AL151" t="s">
         <v>840</v>
-      </c>
-      <c r="AL151" t="s">
-        <v>839</v>
       </c>
       <c r="AM151" t="s">
         <v>112</v>
       </c>
       <c r="AN151" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AO151" t="n">
         <v>36</v>
       </c>
       <c r="AP151" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AQ151" t="s">
         <v>594</v>
@@ -24777,10 +24780,10 @@
       <c r="AV151"/>
       <c r="AW151"/>
       <c r="AX151" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="AY151" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AZ151" t="n">
         <v>648970</v>
@@ -24795,7 +24798,7 @@
         <v>151</v>
       </c>
       <c r="C152" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D152" t="n">
         <v>1487900.5</v>
@@ -24807,7 +24810,7 @@
         <v>93</v>
       </c>
       <c r="G152" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H152" t="s">
         <v>91</v>
@@ -24819,7 +24822,7 @@
         <v>2026</v>
       </c>
       <c r="K152" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L152" t="s">
         <v>95</v>
@@ -24847,7 +24850,7 @@
         <v>101</v>
       </c>
       <c r="W152" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="X152" t="s">
         <v>103</v>
@@ -24866,41 +24869,41 @@
         <v>175</v>
       </c>
       <c r="AD152" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AE152" t="s">
+        <v>1048</v>
+      </c>
+      <c r="AF152" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AG152" t="s">
         <v>1046</v>
       </c>
-      <c r="AE152" t="s">
-        <v>1047</v>
-      </c>
-      <c r="AF152" t="s">
-        <v>1048</v>
-      </c>
-      <c r="AG152" t="s">
-        <v>1045</v>
-      </c>
       <c r="AH152" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AI152" t="n">
         <v>6</v>
       </c>
       <c r="AJ152"/>
       <c r="AK152" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AL152" t="s">
         <v>1050</v>
-      </c>
-      <c r="AL152" t="s">
-        <v>1049</v>
       </c>
       <c r="AM152" t="s">
         <v>112</v>
       </c>
       <c r="AN152" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AO152" t="n">
         <v>1</v>
       </c>
       <c r="AP152" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AQ152" t="s">
         <v>594</v>
@@ -24912,10 +24915,10 @@
       <c r="AV152"/>
       <c r="AW152"/>
       <c r="AX152" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AY152" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="AZ152" t="n">
         <v>1487900</v>
@@ -24930,7 +24933,7 @@
         <v>152</v>
       </c>
       <c r="C153" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D153" t="n">
         <v>1933055.55</v>
@@ -24942,7 +24945,7 @@
         <v>93</v>
       </c>
       <c r="G153" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H153" t="s">
         <v>91</v>
@@ -24954,7 +24957,7 @@
         <v>2026</v>
       </c>
       <c r="K153" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L153" t="s">
         <v>95</v>
@@ -24982,7 +24985,7 @@
         <v>101</v>
       </c>
       <c r="W153" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="X153" t="s">
         <v>103</v>
@@ -25001,41 +25004,41 @@
         <v>175</v>
       </c>
       <c r="AD153" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AE153" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AF153" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="AG153" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AH153" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AI153" t="n">
         <v>6</v>
       </c>
       <c r="AJ153"/>
       <c r="AK153" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AL153" t="s">
         <v>1050</v>
-      </c>
-      <c r="AL153" t="s">
-        <v>1049</v>
       </c>
       <c r="AM153" t="s">
         <v>112</v>
       </c>
       <c r="AN153" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AO153" t="n">
         <v>2</v>
       </c>
       <c r="AP153" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AQ153" t="s">
         <v>594</v>
@@ -25047,10 +25050,10 @@
       <c r="AV153"/>
       <c r="AW153"/>
       <c r="AX153" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AY153" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="AZ153" t="n">
         <v>2092916</v>
@@ -25077,7 +25080,7 @@
         <v>93</v>
       </c>
       <c r="G154" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H154" t="s">
         <v>91</v>
@@ -25089,7 +25092,7 @@
         <v>2026</v>
       </c>
       <c r="K154" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L154" t="s">
         <v>95</v>
@@ -25117,7 +25120,7 @@
         <v>101</v>
       </c>
       <c r="W154" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="X154" t="s">
         <v>103</v>
@@ -25136,41 +25139,41 @@
         <v>175</v>
       </c>
       <c r="AD154" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="AE154" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AF154" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="AG154" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AH154" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AI154" t="n">
         <v>6</v>
       </c>
       <c r="AJ154"/>
       <c r="AK154" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AL154" t="s">
         <v>1050</v>
-      </c>
-      <c r="AL154" t="s">
-        <v>1049</v>
       </c>
       <c r="AM154" t="s">
         <v>112</v>
       </c>
       <c r="AN154" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AO154" t="n">
         <v>3</v>
       </c>
       <c r="AP154" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AQ154" t="s">
         <v>594</v>
@@ -25182,7 +25185,7 @@
       <c r="AV154"/>
       <c r="AW154"/>
       <c r="AX154" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="AY154" t="s">
         <v>180</v>
@@ -25200,7 +25203,7 @@
         <v>154</v>
       </c>
       <c r="C155" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D155" t="n">
         <v>248392</v>
@@ -25212,7 +25215,7 @@
         <v>93</v>
       </c>
       <c r="G155" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H155" t="s">
         <v>91</v>
@@ -25224,7 +25227,7 @@
         <v>2026</v>
       </c>
       <c r="K155" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L155" t="s">
         <v>95</v>
@@ -25252,7 +25255,7 @@
         <v>101</v>
       </c>
       <c r="W155" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="X155" t="s">
         <v>103</v>
@@ -25271,41 +25274,41 @@
         <v>175</v>
       </c>
       <c r="AD155" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AE155" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AF155" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AG155" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AH155" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AI155" t="n">
         <v>6</v>
       </c>
       <c r="AJ155"/>
       <c r="AK155" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AL155" t="s">
         <v>1050</v>
-      </c>
-      <c r="AL155" t="s">
-        <v>1049</v>
       </c>
       <c r="AM155" t="s">
         <v>112</v>
       </c>
       <c r="AN155" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AO155" t="n">
         <v>4</v>
       </c>
       <c r="AP155" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AQ155" t="s">
         <v>594</v>
@@ -25317,10 +25320,10 @@
       <c r="AV155"/>
       <c r="AW155"/>
       <c r="AX155" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="AY155" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="AZ155" t="n">
         <v>276852</v>
@@ -25335,7 +25338,7 @@
         <v>155</v>
       </c>
       <c r="C156" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D156" t="n">
         <v>1956107.51</v>
@@ -25347,7 +25350,7 @@
         <v>93</v>
       </c>
       <c r="G156" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H156" t="s">
         <v>91</v>
@@ -25359,7 +25362,7 @@
         <v>2026</v>
       </c>
       <c r="K156" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L156" t="s">
         <v>95</v>
@@ -25387,7 +25390,7 @@
         <v>101</v>
       </c>
       <c r="W156" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="X156" t="s">
         <v>103</v>
@@ -25406,41 +25409,41 @@
         <v>175</v>
       </c>
       <c r="AD156" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AE156" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AF156" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AG156" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AH156" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AI156" t="n">
         <v>6</v>
       </c>
       <c r="AJ156"/>
       <c r="AK156" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AL156" t="s">
         <v>1050</v>
-      </c>
-      <c r="AL156" t="s">
-        <v>1049</v>
       </c>
       <c r="AM156" t="s">
         <v>112</v>
       </c>
       <c r="AN156" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AO156" t="n">
         <v>5</v>
       </c>
       <c r="AP156" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AQ156" t="s">
         <v>594</v>
@@ -25452,10 +25455,10 @@
       <c r="AV156"/>
       <c r="AW156"/>
       <c r="AX156" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="AY156" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AZ156" t="n">
         <v>1957000</v>
@@ -25470,7 +25473,7 @@
         <v>156</v>
       </c>
       <c r="C157" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D157" t="n">
         <v>1426587.21</v>
@@ -25482,7 +25485,7 @@
         <v>93</v>
       </c>
       <c r="G157" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H157" t="s">
         <v>91</v>
@@ -25494,7 +25497,7 @@
         <v>2026</v>
       </c>
       <c r="K157" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L157" t="s">
         <v>95</v>
@@ -25522,7 +25525,7 @@
         <v>601</v>
       </c>
       <c r="W157" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="X157" t="s">
         <v>103</v>
@@ -25541,41 +25544,41 @@
         <v>436</v>
       </c>
       <c r="AD157" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AE157" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AF157" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="AG157" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AH157" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AI157" t="n">
         <v>6</v>
       </c>
       <c r="AJ157"/>
       <c r="AK157" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AL157" t="s">
         <v>1050</v>
-      </c>
-      <c r="AL157" t="s">
-        <v>1049</v>
       </c>
       <c r="AM157" t="s">
         <v>112</v>
       </c>
       <c r="AN157" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AO157" t="n">
         <v>6</v>
       </c>
       <c r="AP157" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AQ157" t="s">
         <v>594</v>
@@ -25587,10 +25590,10 @@
       <c r="AV157"/>
       <c r="AW157"/>
       <c r="AX157" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AY157" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AZ157" t="n">
         <v>4800000</v>
@@ -25605,7 +25608,7 @@
         <v>157</v>
       </c>
       <c r="C158" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D158" t="n">
         <v>634611.04</v>
@@ -25617,7 +25620,7 @@
         <v>93</v>
       </c>
       <c r="G158" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H158" t="s">
         <v>91</v>
@@ -25629,16 +25632,16 @@
         <v>2026</v>
       </c>
       <c r="K158" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="L158" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M158" t="s">
         <v>96</v>
       </c>
       <c r="N158" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O158" t="s">
         <v>98</v>
@@ -25657,7 +25660,7 @@
         <v>601</v>
       </c>
       <c r="W158" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="X158" t="s">
         <v>103</v>
@@ -25673,10 +25676,10 @@
       </c>
       <c r="AB158"/>
       <c r="AC158" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AD158" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AE158"/>
       <c r="AF158"/>
@@ -25687,15 +25690,15 @@
       <c r="AK158"/>
       <c r="AL158"/>
       <c r="AM158" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN158"/>
       <c r="AO158"/>
       <c r="AP158" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AQ158" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR158"/>
       <c r="AS158"/>
@@ -25704,10 +25707,10 @@
       <c r="AV158"/>
       <c r="AW158"/>
       <c r="AX158" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AY158" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="AZ158" t="n">
         <v>633908</v>
@@ -25734,7 +25737,7 @@
         <v>91</v>
       </c>
       <c r="G159" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H159" t="s">
         <v>91</v>
@@ -25746,16 +25749,16 @@
         <v>2026</v>
       </c>
       <c r="K159" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="L159" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M159" t="s">
         <v>96</v>
       </c>
       <c r="N159" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O159" t="s">
         <v>98</v>
@@ -25790,10 +25793,10 @@
       </c>
       <c r="AB159"/>
       <c r="AC159" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="AD159" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="AE159"/>
       <c r="AF159"/>
@@ -25804,15 +25807,15 @@
       <c r="AK159"/>
       <c r="AL159"/>
       <c r="AM159" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN159"/>
       <c r="AO159"/>
       <c r="AP159" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="AQ159" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR159"/>
       <c r="AS159"/>
@@ -25821,7 +25824,7 @@
       <c r="AV159"/>
       <c r="AW159"/>
       <c r="AX159" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="AY159" t="s">
         <v>216</v>
@@ -25839,7 +25842,7 @@
         <v>159</v>
       </c>
       <c r="C160" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D160" t="n">
         <v>249834</v>
@@ -25851,7 +25854,7 @@
         <v>93</v>
       </c>
       <c r="G160" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H160" t="s">
         <v>91</v>
@@ -25863,16 +25866,16 @@
         <v>2026</v>
       </c>
       <c r="K160" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="L160" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M160" t="s">
         <v>96</v>
       </c>
       <c r="N160" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O160" t="s">
         <v>98</v>
@@ -25910,7 +25913,7 @@
         <v>425</v>
       </c>
       <c r="AD160" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AE160"/>
       <c r="AF160"/>
@@ -25921,15 +25924,15 @@
       <c r="AK160"/>
       <c r="AL160"/>
       <c r="AM160" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN160"/>
       <c r="AO160"/>
       <c r="AP160" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="AQ160" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR160"/>
       <c r="AS160"/>
@@ -25938,10 +25941,10 @@
       <c r="AV160"/>
       <c r="AW160"/>
       <c r="AX160" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="AY160" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AZ160" t="n">
         <v>249834</v>
@@ -25968,7 +25971,7 @@
         <v>93</v>
       </c>
       <c r="G161" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H161" t="s">
         <v>91</v>
@@ -25980,16 +25983,16 @@
         <v>2026</v>
       </c>
       <c r="K161" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="L161" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M161" t="s">
         <v>96</v>
       </c>
       <c r="N161" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O161" t="s">
         <v>98</v>
@@ -26024,10 +26027,10 @@
       </c>
       <c r="AB161"/>
       <c r="AC161" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AD161" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AE161"/>
       <c r="AF161"/>
@@ -26038,15 +26041,15 @@
       <c r="AK161"/>
       <c r="AL161"/>
       <c r="AM161" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN161"/>
       <c r="AO161"/>
       <c r="AP161" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AQ161" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR161" t="s">
         <v>154</v>
@@ -26061,7 +26064,7 @@
       <c r="AV161"/>
       <c r="AW161"/>
       <c r="AX161" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="AY161" t="s">
         <v>368</v>
@@ -26091,7 +26094,7 @@
         <v>93</v>
       </c>
       <c r="G162" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H162" t="s">
         <v>91</v>
@@ -26103,16 +26106,16 @@
         <v>2026</v>
       </c>
       <c r="K162" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="L162" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M162" t="s">
         <v>96</v>
       </c>
       <c r="N162" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O162" t="s">
         <v>98</v>
@@ -26147,10 +26150,10 @@
       </c>
       <c r="AB162"/>
       <c r="AC162" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="AD162" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="AE162"/>
       <c r="AF162"/>
@@ -26161,15 +26164,15 @@
       <c r="AK162"/>
       <c r="AL162"/>
       <c r="AM162" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN162"/>
       <c r="AO162"/>
       <c r="AP162" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AQ162" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR162"/>
       <c r="AS162"/>
@@ -26178,7 +26181,7 @@
       <c r="AV162"/>
       <c r="AW162"/>
       <c r="AX162" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="AY162" t="s">
         <v>666</v>
@@ -26196,19 +26199,19 @@
         <v>162</v>
       </c>
       <c r="C163" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D163" t="n">
         <v>327803</v>
       </c>
       <c r="E163" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F163" t="s">
         <v>93</v>
       </c>
       <c r="G163" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H163" t="s">
         <v>91</v>
@@ -26220,16 +26223,16 @@
         <v>2026</v>
       </c>
       <c r="K163" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="L163" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M163" t="s">
         <v>96</v>
       </c>
       <c r="N163" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O163" t="s">
         <v>98</v>
@@ -26239,7 +26242,7 @@
       <c r="R163"/>
       <c r="S163"/>
       <c r="T163" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="U163" t="s">
         <v>100</v>
@@ -26264,10 +26267,10 @@
       </c>
       <c r="AB163"/>
       <c r="AC163" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AD163" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AE163"/>
       <c r="AF163"/>
@@ -26278,7 +26281,7 @@
       <c r="AK163"/>
       <c r="AL163"/>
       <c r="AM163" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN163"/>
       <c r="AO163"/>
@@ -26286,7 +26289,7 @@
         <v>706</v>
       </c>
       <c r="AQ163" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR163"/>
       <c r="AS163"/>
@@ -26295,10 +26298,10 @@
       <c r="AV163"/>
       <c r="AW163"/>
       <c r="AX163" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AY163" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AZ163" t="n">
         <v>327803</v>
@@ -26313,7 +26316,7 @@
         <v>163</v>
       </c>
       <c r="C164" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D164" t="n">
         <v>5000000</v>
@@ -26325,7 +26328,7 @@
         <v>93</v>
       </c>
       <c r="G164" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H164" t="s">
         <v>91</v>
@@ -26337,16 +26340,16 @@
         <v>2026</v>
       </c>
       <c r="K164" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="L164" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M164" t="s">
         <v>96</v>
       </c>
       <c r="N164" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O164" t="s">
         <v>98</v>
@@ -26381,10 +26384,10 @@
       </c>
       <c r="AB164"/>
       <c r="AC164" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="AD164" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AE164"/>
       <c r="AF164"/>
@@ -26395,7 +26398,7 @@
       <c r="AK164"/>
       <c r="AL164"/>
       <c r="AM164" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN164"/>
       <c r="AO164"/>
@@ -26403,7 +26406,7 @@
         <v>706</v>
       </c>
       <c r="AQ164" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR164"/>
       <c r="AS164"/>
@@ -26412,10 +26415,10 @@
       <c r="AV164"/>
       <c r="AW164"/>
       <c r="AX164" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="AY164" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="AZ164" t="n">
         <v>5000000</v>
@@ -26430,19 +26433,19 @@
         <v>164</v>
       </c>
       <c r="C165" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D165" t="n">
         <v>1271512.04</v>
       </c>
       <c r="E165" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F165" t="s">
         <v>93</v>
       </c>
       <c r="G165" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H165" t="s">
         <v>91</v>
@@ -26454,16 +26457,16 @@
         <v>2026</v>
       </c>
       <c r="K165" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="L165" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M165" t="s">
         <v>96</v>
       </c>
       <c r="N165" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O165" t="s">
         <v>98</v>
@@ -26473,7 +26476,7 @@
       <c r="R165"/>
       <c r="S165"/>
       <c r="T165" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="U165" t="s">
         <v>100</v>
@@ -26482,7 +26485,7 @@
         <v>101</v>
       </c>
       <c r="W165" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="X165" t="s">
         <v>103</v>
@@ -26498,10 +26501,10 @@
       </c>
       <c r="AB165"/>
       <c r="AC165" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AD165" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="AE165"/>
       <c r="AF165"/>
@@ -26512,15 +26515,15 @@
       <c r="AK165"/>
       <c r="AL165"/>
       <c r="AM165" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN165"/>
       <c r="AO165"/>
       <c r="AP165" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="AQ165" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR165"/>
       <c r="AS165"/>
@@ -26529,10 +26532,10 @@
       <c r="AV165"/>
       <c r="AW165"/>
       <c r="AX165" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="AY165" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="AZ165" t="n">
         <v>2382927</v>
@@ -26547,19 +26550,19 @@
         <v>165</v>
       </c>
       <c r="C166" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D166" t="n">
         <v>976255</v>
       </c>
       <c r="E166" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F166" t="s">
         <v>93</v>
       </c>
       <c r="G166" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H166" t="s">
         <v>91</v>
@@ -26571,16 +26574,16 @@
         <v>2026</v>
       </c>
       <c r="K166" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="L166" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M166" t="s">
         <v>96</v>
       </c>
       <c r="N166" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O166" t="s">
         <v>98</v>
@@ -26590,7 +26593,7 @@
       <c r="R166"/>
       <c r="S166"/>
       <c r="T166" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="U166" t="s">
         <v>100</v>
@@ -26599,7 +26602,7 @@
         <v>101</v>
       </c>
       <c r="W166" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="X166" t="s">
         <v>103</v>
@@ -26615,10 +26618,10 @@
       </c>
       <c r="AB166"/>
       <c r="AC166" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="AD166" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="AE166"/>
       <c r="AF166"/>
@@ -26629,15 +26632,15 @@
       <c r="AK166"/>
       <c r="AL166"/>
       <c r="AM166" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN166"/>
       <c r="AO166"/>
       <c r="AP166" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AQ166" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR166"/>
       <c r="AS166"/>
@@ -26646,10 +26649,10 @@
       <c r="AV166"/>
       <c r="AW166"/>
       <c r="AX166" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AY166" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AZ166" t="n">
         <v>976255</v>
@@ -26664,7 +26667,7 @@
         <v>166</v>
       </c>
       <c r="C167" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D167" t="n">
         <v>194472</v>
@@ -26676,7 +26679,7 @@
         <v>93</v>
       </c>
       <c r="G167" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H167" t="s">
         <v>91</v>
@@ -26688,16 +26691,16 @@
         <v>2026</v>
       </c>
       <c r="K167" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="L167" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M167" t="s">
         <v>96</v>
       </c>
       <c r="N167" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O167" t="s">
         <v>98</v>
@@ -26716,7 +26719,7 @@
         <v>601</v>
       </c>
       <c r="W167" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="X167" t="s">
         <v>103</v>
@@ -26735,7 +26738,7 @@
         <v>436</v>
       </c>
       <c r="AD167" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="AE167"/>
       <c r="AF167"/>
@@ -26746,15 +26749,15 @@
       <c r="AK167"/>
       <c r="AL167"/>
       <c r="AM167" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN167"/>
       <c r="AO167"/>
       <c r="AP167" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="AQ167" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR167"/>
       <c r="AS167"/>
@@ -26763,10 +26766,10 @@
       <c r="AV167"/>
       <c r="AW167"/>
       <c r="AX167" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="AY167" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="AZ167" t="n">
         <v>202848</v>
@@ -26793,7 +26796,7 @@
         <v>93</v>
       </c>
       <c r="G168" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H168" t="s">
         <v>91</v>
@@ -26805,16 +26808,16 @@
         <v>2026</v>
       </c>
       <c r="K168" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="L168" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M168" t="s">
         <v>96</v>
       </c>
       <c r="N168" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O168" t="s">
         <v>98</v>
@@ -26833,7 +26836,7 @@
         <v>101</v>
       </c>
       <c r="W168" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="X168" t="s">
         <v>103</v>
@@ -26849,10 +26852,10 @@
       </c>
       <c r="AB168"/>
       <c r="AC168" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="AD168" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="AE168"/>
       <c r="AF168"/>
@@ -26863,15 +26866,15 @@
       <c r="AK168"/>
       <c r="AL168"/>
       <c r="AM168" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN168"/>
       <c r="AO168"/>
       <c r="AP168" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="AQ168" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AR168"/>
       <c r="AS168"/>
@@ -26880,7 +26883,7 @@
       <c r="AV168"/>
       <c r="AW168"/>
       <c r="AX168" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="AY168" t="s">
         <v>561</v>
@@ -26997,25 +27000,25 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B8" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C8" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D9"/>
     </row>
@@ -27032,22 +27035,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="F1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="G1" t="s">
         <v>46</v>
@@ -27058,7 +27061,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B2" t="n">
         <v>17</v>
@@ -27067,24 +27070,24 @@
         <v>28803045</v>
       </c>
       <c r="D2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="F2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B3" t="n">
         <v>7</v>
@@ -27093,24 +27096,24 @@
         <v>102840000</v>
       </c>
       <c r="D3" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E3" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F3" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="G3" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H3" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B4" t="n">
         <v>10</v>
@@ -27119,24 +27122,24 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E4" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F4" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="G4" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H4" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
@@ -27145,24 +27148,24 @@
         <v>68288726</v>
       </c>
       <c r="D5" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E5" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="F5" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="G5" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H5" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -27171,19 +27174,19 @@
         <v>1935762.88</v>
       </c>
       <c r="D6" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E6" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="G6" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H6" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
   </sheetData>
